--- a/data/ExportedEstimate_22-09-2026.xlsx
+++ b/data/ExportedEstimate_22-09-2026.xlsx
@@ -53,7 +53,7 @@
     <t>West Europe</t>
   </si>
   <si>
-    <t xml:space="preserve">1 B2s (2 Cores, 4 GB RAM) x 72 Horas (Pay as you go), Linux,  (Pay as you go); 0 managed disks – S4; Inter Region transfer type, 5 GB outbound data transfer from Oeste de Europa to Este de Asia</t>
+    <t xml:space="preserve">1 B2ls v2 (2 vCPUs, 4 GB RAM) x 72 Horas (Pay as you go), Linux,  (Pay as you go); 0 managed disks – S4; Inter Region transfer type, 5 GB outbound data transfer from Oeste de Europa to Este de Asia</t>
   </si>
   <si>
     <t>Almacenamiento</t>
@@ -107,7 +107,7 @@
     <t>All prices shown are in Euro Zone – Euro (€) EUR. This is a summary estimate, not a quote. For up to date pricing information please visit https://azure.microsoft.com/pricing/calculator/</t>
   </si>
   <si>
-    <t>This estimate was created at 9/22/2026 11:00:02 AM UTC.</t>
+    <t>This estimate was created at 9/22/2026 12:12:07 PM UTC.</t>
   </si>
 </sst>
 </file>

--- a/data/ExportedEstimate_22-09-2026.xlsx
+++ b/data/ExportedEstimate_22-09-2026.xlsx
@@ -5,7 +5,7 @@
     <workbookView/>
   </bookViews>
   <sheets>
-    <sheet name="Su presupuesto" sheetId="1" r:id="rId1"/>
+    <sheet name="Your Estimate" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>
@@ -17,7 +17,7 @@
     <t>Microsoft Azure Estimate</t>
   </si>
   <si>
-    <t>Su presupuesto</t>
+    <t>Your Estimate</t>
   </si>
   <si>
     <t>Service category</t>
@@ -47,16 +47,16 @@
     <t>Virtual Machines</t>
   </si>
   <si>
-    <t>Mi Máquina Virtual</t>
+    <t>Mi máquina virtual</t>
   </si>
   <si>
-    <t>West Europe</t>
+    <t>Spain Central</t>
   </si>
   <si>
-    <t xml:space="preserve">1 B2ls v2 (2 vCPUs, 4 GB RAM) x 72 Horas (Pay as you go), Linux,  (Pay as you go); 0 managed disks – S4; Inter Region transfer type, 5 GB outbound data transfer from Oeste de Europa to Este de Asia</t>
+    <t xml:space="preserve">1 B2ls v2 (2 vCPUs, 4 GB RAM) x 72 Hours (Pay as you go), Linux,  (Pay as you go); 0 managed disks – S4; Inter Region transfer type, 5 GB outbound data transfer from Spain Central to East Asia</t>
   </si>
   <si>
-    <t>Almacenamiento</t>
+    <t>Storage</t>
   </si>
   <si>
     <t>Managed Disks</t>
@@ -65,19 +65,19 @@
     <t>Mi disco</t>
   </si>
   <si>
-    <t>Managed Disks, SSD estándar, LRS Redundancia, E4 Tipo de disco 1 Discos, Transacciones de Storage: 0; Pago por uso</t>
+    <t>Managed Disks, Standard SSD, LRS Redundancy, E4 Disk Type 1 Disks, 0 Storage transactions; Pay as you go</t>
   </si>
   <si>
-    <t>Redes</t>
+    <t>Networking</t>
   </si>
   <si>
     <t>IP Addresses</t>
   </si>
   <si>
-    <t>Mi Dirección IP</t>
+    <t>Mi dirección IP</t>
   </si>
   <si>
-    <t>Estándar (ARM), 1 direcciones IP estáticas X 72 Horas, 0 prefijos de DIRECCIONES IP públicas X 730 Horas</t>
+    <t>Standard (ARM), 1 Static IP Addresses X 72 Hours, 0 Public IP Prefixes X 730 Hours</t>
   </si>
   <si>
     <t>Support</t>
@@ -107,7 +107,7 @@
     <t>All prices shown are in Euro Zone – Euro (€) EUR. This is a summary estimate, not a quote. For up to date pricing information please visit https://azure.microsoft.com/pricing/calculator/</t>
   </si>
   <si>
-    <t>This estimate was created at 9/22/2026 12:12:07 PM UTC.</t>
+    <t>This estimate was created at 9/22/2026 4:01:39 PM UTC.</t>
   </si>
 </sst>
 </file>
@@ -377,7 +377,7 @@
         <v>13</v>
       </c>
       <c r="F4" s="5">
-        <v>2.9675425038639878</v>
+        <v>2.8191653786707884</v>
       </c>
       <c r="G4" s="5">
         <v>0</v>
@@ -627,7 +627,7 @@
       </c>
       <c r="E11" s="12"/>
       <c r="F11" s="15">
-        <v>5.3374549201442552</v>
+        <v>5.1890777949510571</v>
       </c>
       <c r="G11" s="15">
         <v>0</v>
